--- a/docs/SamuraiData/契約管理.xlsx
+++ b/docs/SamuraiData/契約管理.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ShuKawanami(川波嵩)\Downloads\SamuraiData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dirbato-my.sharepoint.com/personal/shu_kawanami_z616_dirbato_co_jp/Documents/ドキュメント/Samurai/samurai/docs/SamuraiData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30417948-C624-4AAA-B245-CACAB4114D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{30417948-C624-4AAA-B245-CACAB4114D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F18C93-7A84-4671-93F3-37F181506974}"/>
   <bookViews>
-    <workbookView xWindow="-2544" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="契約管理-mapping" sheetId="2" r:id="rId1"/>
